--- a/final-project/check list testing final project IT 215.xlsx
+++ b/final-project/check list testing final project IT 215.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="159">
   <si>
     <t>add_account</t>
   </si>
@@ -299,9 +299,6 @@
     <t>input: id task đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, task có trạng thái chưa bị xóa, tài khoản của người phụ trách không còn hoạt động</t>
   </si>
   <si>
-    <t>input: id task đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, task có trạng thái chưa bị xóa, tài khoản của người phụ trách còn hoạt động</t>
-  </si>
-  <si>
     <t>soft_delete_task</t>
   </si>
   <si>
@@ -357,6 +354,153 @@
   </si>
   <si>
     <t>output: Thông báo thêm comment thành công</t>
+  </si>
+  <si>
+    <t>sort_by_asc</t>
+  </si>
+  <si>
+    <t>output: Trả về một list các task có liên quan đến project id được cung cấp được sắp xếp theo thời gian tạo tăng dần</t>
+  </si>
+  <si>
+    <t>sort_by_desc</t>
+  </si>
+  <si>
+    <t>output: Trả về một list các task có liên quan đến project id được cung cấp được sắp xếp theo thời gian tạo giảm dần</t>
+  </si>
+  <si>
+    <t>Luồng xử lý</t>
+  </si>
+  <si>
+    <t>Khi nhận email, mật khẩu và những thông itn cá nhân khác từ schema, tìm kiếm sự tồn tại của email được truyền vào trong bảng lưu thông tin các tài khoản, nếu không tồn tại mật khẩu sẽ kiểm tra độ dài, chứa ít nhất 1 ký tự, 1 chữ viết hoa, một chữ thường, và một số.Sau khi mật khẩu hợp lệ, hash password . Khi tất cả dữ liệu đã hợp lệ thì add, commit và refresh cho database.</t>
+  </si>
+  <si>
+    <t>Nhận vào keyword và status keyword từ query parameter, trong trường hợp cả hai giá trị nhận vào là None thì trả về toàn bộ danh sách các tài khoản, trường hợp chỉ nhận vào keyword, sử dụng filter + ilike để tìm kiếm tên tài khoản/email của tài khoản có liên quan đến keyword, trường hợp chỉ nhận status keyword, dùng filter để so sánh trạng thái của tài khoản với trạng thái được nhận từ query. Trường hợp nhận cả 2 sử dụng filter + ilike và so sánh status để lấy tất cả kết quả tương tự. Chức năng chỉ hoạt động khi tài khoản đang thao tác có role là admin.</t>
+  </si>
+  <si>
+    <t>handle_token</t>
+  </si>
+  <si>
+    <t>Sử dụng http bearer làm security key, http authorization để lấy thông tin xác thực, giải mã access token thông qua jwt decode, từ đó trả về thông tin dưới dạng dict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output: Thông tin tài khoản được truyền vào trong access token khi đăng nhập tài khoản </t>
+  </si>
+  <si>
+    <t>input: access token chưa hết hạn</t>
+  </si>
+  <si>
+    <t>input: access token đã hết hạn</t>
+  </si>
+  <si>
+    <t>output: lỗi 401</t>
+  </si>
+  <si>
+    <t>Khi nhận vào email và mật khẩu từ schema, tìm kiếm sự tồn tại của email tròn bảng lưu thông tin của các tài khoản, nếu email tồn tại, kiểm tra mật khẩu thông qua checkpw so sánh mật khẩu đã được hash trong database so với mật khẩu vừa được nhận từ schema, nếu đúng, cung cấp token, loại token và thời gian hết hạn để đăng nhập cho tài khoản thông qua jwt encode chỉ trong trường hợp tài khoản còn hoạt động</t>
+  </si>
+  <si>
+    <t>Nhận vào các thông tin cơ bản của project, trường hợp tên project được cung cấp đã được tạo, thông báo lỗi. Trường hợp còn tại, tiến hành tạo một project mới với trạng thái xóa là false cùng với ngày tạo là datetime now, tự động điền id của người dùng đang thao tác vào owner id sử dụng db add, commit, refresh để thêm dữ liệu lưu, và tải lại dữ liệu, cùng với đó tự động thêm một project member mới với vai trò owner và project id của project vừa được khởi tạo, sử dụng db.add, commit để thêm dữ liệu vào bảng project member</t>
+  </si>
+  <si>
+    <t>Nhận vào keyword từ Query, nếu không truyền dữ liệu, query vào bảng project member, lấy dữ liệu với điều kiện project member có id trùng khớp với id của người dùng đang thao tác, trả về tất cả những dữ liệu được tìm thấy, trường hợp nhận được thông tin từ keyword,  query đến bảng Project, join bảng project member thông qua project id, sử dụng filter+  ilike để lấy thông tin của project có tên gần giống với keyword được nhận, trả về toàn bộ thông tin tìm thấy, trường hợp không itmg thấy, trả về lỗi 404</t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path paramete, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project với điều kiện id của project trùng khớp với project id được truyền vào từ path parameter , trường hợp không tìm thấy thông tin project, trả về mã lỗi 404, trường hợp không đủ quyền, trả về mã lỗi 403</t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path paramete, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project để tìm kiếm thông tin project cần cập nhật thông tin thông qua id, trong trường hợp tìm thấy, kiểm tra nếu project chưa bị xóa, sử dụng model dump + exculde unset = True vào schema cập nhật project để lấy những thông tin được nhập liệu, query đến bảng project kiểm tra tên project mới được cung cấp có trùng với những project có id khác với project id được nhận vào từ path parameter hay không, nếu không, sử dụng vòng lặp for key, item trong biến lưu model dump của schema cập nhật + setattr để cập nhật lại dữ liệu, sử dụng db commit và refresh để lưu chỉnh sửa và tải lại dữ liệu và trả về dữ liệu sau cập nhật, trường hợp tên trùng / project đã bị xóa, trả về lỗi 400, trường hợp không trong project / không đủ quyền hạn, trả về lỗi 403, trường hợp không tìm thấy project trả về lỗi 404</t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project để tìm kiếm thông tin project cần thực hiện xóa mềm qua project id được nhận từ path parameter trong trường hợp tìm thấy thông tin project, kiểm tra trạng thái xem project đã bị xóa hay chưa, nếu chưa, đổi trạng thái project thành đã bị xóa và trả về mã 204 theo đó,đổi tất cả trạng thái của task và project member có liên quan đến project này thành đã xóa thông qua vòng lặp for, nếu project bị xóa rồi, trả về lỗi 400, trong trường hợp không itmf thấy project trả về lỗi 404, trong trường hợp người dùng không có trong project/không đủ quyên thực hiện chức năng trả về lỗi 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project để tìm kiếm thông tin project cần thêm thành viên, nếu không tìm thấy project trả về mã lỗi 404, nếu không đủ quyền thao tác/ người dùng không nằm trong project thao tác trả về lỗi 403, nếu project vẫn còn hoạt động query đến bảng user để tìm kiếm user theo user id được nhận từ schema nếu tìm được user và user vẫn còn hoạt động thì thêm dữ liệu mới cho project member với role mặc định là member và trả về thông tin của project member mới thêm, trạng thái mặc định là chưa xóa, nếu như người dùng được thêm đã bị xóa/ project đã bị xóa trả lỗi 403, nếu không tìm thấy người được thêm thì trả lỗi 404, Trong trường hợp người dùng đã tồn tại trong project member với project id trùng với project id được nhận và chưa bị xóa thì trả về lỗi 400 trường hợp có trạng thái bị xóa thì gán lại trạng thái thành chưa xóa và trả về thông báo thêm thành công </t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project member để tìm kiếm thông tin project member cần xem thành viên, nếu người dùng không đủ quyền thực hiện chức năng/không tồn tại trong project trả lỗi 403, trong trường hợp không tìm thấy project member có liên quan đến dự án trả về lỗi 404, nếu tìm thấy trả về tất cả dữ liệu được tìm thấy trong project member</t>
+  </si>
+  <si>
+    <t>Nhận vào id của project, project member thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project member để tìm kiếm thông tin project member cần xóa thành viên, trong trường hợp người dùng không đủ quyền hạn thao tác/không nằm trong project, trả về mã lỗi 403, trong trường hợp không tìm thấy project member có project id trùng với project id được cung cấp, user id trùng khớp với user id được nhận trả về mã lỗi 404, trường hợp tìm thấy, kiểm tra trạng thái của project member xem bị xóa chưa, nếu chưa thì đổi trạng thái của project member đó thành đã xóa, nếu xóa rồi thì trả mã lỗi 400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng project để tìm kiếm project cần thêm task, trong trường hợp người thao tác không đủ quyền hạn/không thuộc project trả về lỗi 403, trong trường hợp không tìm thấy project cần thêm task, trả về lỗi 404, trường hợp project đã bị xóa, trả về lỗi 400 trường hợp task bị đặt trùng tên với task đã tồn tại trong cùng một project, trả về mã lôi 400, ngược lại tiến hành tạo một task mới với trạng thái chưa bị xóa, ngày tạo lấy datetime now, id người phụ trách đặt là None, add, commit, refresh để thêm thông tin vào bảng task, lưu dữ liệu, tải lại dữ liệu, trả về thông tin của task vừa được thêm vào database </t>
+  </si>
+  <si>
+    <t>Nhận vào id của task thông qua path parameter, nhận vào thông tin của người đang theo tác thông qua dependency + Depends, tìm tiếm task có id trùng khớp với task id nhận được từ schema, trường hợp không tìm thấy trả về lỗi 404, trường hợp tìm thấy sử dụng biến chứa thông tin để lấy thông tin về trường project id của task tìm được, từ đó kiểm tra role của người dùng hiện tại nếu như role không đáp ứng/người dùng không tồn tại trong project trả về lỗi 403, ngược lại, trả về thông tin của task với id trùng khớp với task id nhận được từ schema</t>
+  </si>
+  <si>
+    <t>show_tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output: tất cả các task có project id trùng khớp với project id nhận được </t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng task để tìm kiếm task có project id trùng khớp với project id nhận được từ schema, nếu tìm thấy, trả về tất cả các task có liên quan, trường hợp không tìm thấy, trả về mã lỗi 404, trường hợp người dùng không đủ quyền thực hiện chức năng/không tồn tại trong project trả lỗi 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input: id task đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, task có trạng thái chưa bị xóa, tài khoản của người phụ trách còn hoạt động và thuộc dự án </t>
+  </si>
+  <si>
+    <t xml:space="preserve">input: id task đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, task có trạng thái chưa bị xóa, tài khoản của người phụ trách còn hoạt động và không thuộc dự án </t>
+  </si>
+  <si>
+    <t>Nhận vào id của task thông qua path parameter, nhận vào thông tin của người đang theo tác thông qua dependency + Depends, tìm tiếm task có id trùng khớp với task id nhận được từ schema, trường hợp không tìm thấy trả về lỗi 404, trường hợp tìm thấy sử dụng biến chứa thông tin để lấy thông tin về trường project id của task tìm được, từ đó kiểm tra role của người dùng hiện tại nếu như role không đáp ứng/người dùng không tồn tại trong project trả về lỗi 403, trường hợp thêm id của người phụ trách không còn hoạt động, trả về lỗi 400, trường hợp người dùng được thêm trong id người phụ trách không thuộc dự án, trả mã lỗi 403, trong trường hợp task đã bị xóa trả lỗi 400,ngược lại  sử dụng vòng lặp for key, item trong biến lưu model dump của schema cập nhật + setattr để cập nhật lại dữ liệu, sử dụng db commit và refresh để lưu chỉnh sửa và tải lại dữ liệu và trả về dữ liệu sau cập nhật</t>
+  </si>
+  <si>
+    <t>Nhận vào id của task thông qua path parameter, nhận vào thông tin của người đang theo tác thông qua dependency + Depends, tìm tiếm task có id trùng khớp với task id nhận được từ schema, trường hợp không tìm thấy trả về lỗi 404, trường hợp tìm thấy sử dụng biến chứa thông tin để lấy thông tin về trường project id của task tìm được, từ đó kiểm tra role của người dùng hiện tại nếu như role không đáp ứng/người dùng không tồn tại trong project trả về lỗi 403, trường hợp project có trạng thái đã bị xóa, trả về mã lỗi 400, ngược lại, gán lại trạng thái cho task là đã bị xóa, trả về mã 204</t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path parameter,keyword thông qua query parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng task để tìm kiếm task có project id trùng khớp với project id nhận được từ schema, trường hợp người dùng không đủ quyền thao tác/không tồn tại trong project trả lỗi 403, nếu không nhận được dữ liệu từ keyword, trả hết tất cả các task có project id trùng khớp với project id nhận được từ path parameter, trường hợp nhận được keyword, sử dụng filter+ilike để tìm kiếm tên task, thứ tự ưu tiên của task, trạng thái, id của người phụ trách có liên quan đến keyword nhận được từ query parameter và trả về task có liên quan và có project id trùng khớp với project id nhận được, trường hợp không tìm thấy thông tin trả lỗi 404</t>
+  </si>
+  <si>
+    <t>Nhận vào id của task thông qua path parameter, nhận vào thông tin của người đang theo tác thông qua dependency + Depends, tìm tiếm task có id trùng khớp với task id nhận được từ schema, trường hợp không tìm thấy trả về lỗi 404, trường hợp tìm thấy sử dụng biến chứa thông tin để lấy thông tin về trường project id của task tìm được, từ đó kiểm tra role của người dùng hiện tại nếu như role không đáp ứng/người dùng không tồn tại trong project trả về lỗi 403, trường hợp project có trạng thái đã bị xóa, trả về mã lỗi 400, trường hợp file tải lên không đúng định dạng quy đinh, trả về mã lỗi 400, ngược lại thông báo thêm file thành công vào task</t>
+  </si>
+  <si>
+    <t>input: id projectđúng, người dùng đáp ứng role của chức năng và tồn tại trong project, project chưa bị xóa</t>
+  </si>
+  <si>
+    <t>input: id project đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, project chưa bị xóa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">input: id project đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, không tìm thấy task liên quan đến project </t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng task để tìm kiếm task có project id trùng khớp với project id nhận được từ schema, nếu tìm thấy, trả về tất cả các task có liên quan được sắp xếp theo thứ tự tăng dần bằng order by+ asc, trường hợp không tìm thấy, trả về mã lỗi 404, trường hợp người dùng không đủ quyền thực hiện chức năng/không tồn tại trong project trả lỗi 403</t>
+  </si>
+  <si>
+    <t>Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng task để tìm kiếm task có project id trùng khớp với project id nhận được từ schema, nếu tìm thấy, trả về tất cả các task có liên quan được sắp xếp theo thứ tự giảm dần bằng order by+ desc, trường hợp không tìm thấy, trả về mã lỗi 404, trường hợp người dùng không đủ quyền thực hiện chức năng/không tồn tại trong project trả lỗi 403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận vào id của task thông qua path parameter, nhận vào thông tin của người đang theo tác thông qua dependency + Depends, tìm tiếm task có id trùng khớp với task id nhận được từ schema, trường hợp không tìm thấy trả về lỗi 404, trường hợp tìm thấy sử dụng biến chứa thông tin để lấy thông tin về trường project id của task tìm được, từ đó kiểm tra role của người dùng hiện tại nếu như role không đáp ứng/người dùng không tồn tại trong project trả về lỗi 403, trường hợp task đã bị xóa, trả về mã lôi 400, trường hợp người thêm comment đã bị xóa khỏi project member trả về lỗi 400, ngược lại, tạo một comment mới, sử udnjg db add, commit,refresh để thêm, lưu, tải lại dữ liệu và thông báo thêm comment thành công cho task </t>
+  </si>
+  <si>
+    <t>limit_offsett</t>
+  </si>
+  <si>
+    <t>input: id project đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, không nhập limit data và offsett data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output: danh sách tất cả các task có liên quan đến project id được cung cấp </t>
+  </si>
+  <si>
+    <t>input: id project đúng, người dùng đáp ứng role của chức năng và tồn tại trong project,  nhập limit data, không nhập offsett data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output: danh sách tất cả các task có liên quan đến project id được cung cấp và giới hạn hiển thị số lượng dữ liệu theo limit data được cung cấp </t>
+  </si>
+  <si>
+    <t>input: id project đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, không nhập limit data, nhập offsett data</t>
+  </si>
+  <si>
+    <t>output: danh sách tất cả các task có liên quan đến project id được cung cấp và bỏ qua số lượng dữ liệu theo offsett data được cung cấp</t>
+  </si>
+  <si>
+    <t>input: id project đúng, người dùng đáp ứng role của chức năng và tồn tại trong project, nhập limit data và offsett data</t>
+  </si>
+  <si>
+    <t>output: danh sách tất cả các task có liên quan đến project id được cung cấp và giới hạn hiển thị số lượng dữ liệu theo limit data được cung cấp cùng bỏ qua số lượng dữ liệu theo offsett data được cung cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhận vào id của project thông qua path parameter, lấy dữ liệu của người dùng đang thao tác thông qua dependency + Depends, query đến bảng project member để kiểm tra thông tin của người dùng trong project nếu tìm thấy người dùng và người dùng đáp ứng được role cần thiết để thao tác trên chức năng này, query đến bảng task để tìm kiếm task có project id trùng khớp với project id nhận được từ schema, trường hợp người dùng không đủ quyền hạn thao tác/không thuộc project trả về mã lỗi 403, không tìm thấy project, trả về mã lỗi 404, trường hợp không nhập gì vào limit data và offsett data, sử dụng query đến bảng task và hiển thị tất cả các task có project id trùng khớp với project id nhận vào từ path parameter, trường hợp chỉ nhận dữ liệu từ limit data, query đến bảng task, hiển thị tất cả các task có project id liên quan sử dụng limit và truyền limit data vào để giới hạn số lượng dữ liệu hiển thị, trường hợp chỉ nhận dữ liệu từ offsett data, query đến bảng task, hiển thị tất cả các task có project id liên quan sử dụng offsett và truyền offsett data vào để bỏ qua số lượng dữ liệu nhất định,  trường hợp nhận dữ liệu từ limit data và offsett data , query đến bảng task, hiển thị tất cả các task có project id liên quan sử dụng limit và truyền limit data vào để giới hạn số lượng dữ liệu hiển thị và sử dụng offsett và truyền offsett data vào để bỏ qua số lượng dữ liệu nhất định, trường hợp dữ liệu trả về None, trả về lỗi 404, trường hợp limit nhập quá 50 tự động gán lại giá trị limit về 50 </t>
   </si>
 </sst>
 </file>
@@ -397,7 +541,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -457,11 +601,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -472,6 +625,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -489,9 +645,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,32 +947,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="183.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="162.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.88671875" customWidth="1"/>
+    <col min="3" max="3" width="49.44140625" customWidth="1"/>
+    <col min="4" max="4" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
-    </row>
-    <row r="2" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-    </row>
-    <row r="4" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>50</v>
       </c>
@@ -807,18 +986,23 @@
       <c r="C4" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D4" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
@@ -828,8 +1012,11 @@
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D7" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3"/>
       <c r="B8" s="1" t="s">
         <v>2</v>
@@ -837,8 +1024,9 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="1" t="s">
         <v>48</v>
@@ -846,9 +1034,10 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -857,27 +1046,32 @@
       <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
+      <c r="D10" s="6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
       <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="8"/>
+      <c r="D11" s="6"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
       <c r="B12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -886,84 +1080,121 @@
       <c r="C13" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
+      <c r="D13" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="9" t="s">
+      <c r="D14" s="6"/>
+    </row>
+    <row r="15" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="7"/>
-      <c r="B16" s="10"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="9" t="s">
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="3"/>
+      <c r="B17" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7"/>
-      <c r="B18" s="10"/>
+      <c r="D17" s="6"/>
+    </row>
+    <row r="18" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="9" t="s">
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="8"/>
-      <c r="B20" s="10"/>
+      <c r="D19" s="6"/>
+    </row>
+    <row r="20" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="6"/>
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="27" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D20" s="6"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="9"/>
+      <c r="B22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
-    </row>
-    <row r="29" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
-    </row>
-    <row r="30" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
-    </row>
-    <row r="31" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
         <v>50</v>
       </c>
@@ -973,18 +1204,23 @@
       <c r="C31" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D31" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-    </row>
-    <row r="33" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D32" s="5"/>
+    </row>
+    <row r="33" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-    </row>
-    <row r="34" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D33" s="5"/>
+    </row>
+    <row r="34" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>24</v>
       </c>
@@ -994,8 +1230,11 @@
       <c r="C34" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D34" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3"/>
       <c r="B35" s="1" t="s">
         <v>27</v>
@@ -1003,42 +1242,49 @@
       <c r="C35" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D35" s="6"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D36" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3"/>
-      <c r="B37" s="11"/>
+      <c r="B37" s="6"/>
       <c r="C37" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D37" s="6"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3"/>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D38" s="6"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3"/>
-      <c r="B39" s="11"/>
+      <c r="B39" s="6"/>
       <c r="C39" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D39" s="6"/>
+    </row>
+    <row r="40" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>11</v>
       </c>
@@ -1048,8 +1294,11 @@
       <c r="C40" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D40" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3"/>
       <c r="B41" s="1" t="s">
         <v>38</v>
@@ -1057,8 +1306,9 @@
       <c r="C41" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D41" s="6"/>
+    </row>
+    <row r="42" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3"/>
       <c r="B42" s="1" t="s">
         <v>40</v>
@@ -1066,8 +1316,9 @@
       <c r="C42" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3"/>
       <c r="B43" s="1" t="s">
         <v>41</v>
@@ -1075,8 +1326,9 @@
       <c r="C43" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D43" s="6"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
@@ -1086,8 +1338,11 @@
       <c r="C44" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D44" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3"/>
       <c r="B45" s="1" t="s">
         <v>38</v>
@@ -1095,8 +1350,9 @@
       <c r="C45" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D45" s="6"/>
+    </row>
+    <row r="46" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3"/>
       <c r="B46" s="1" t="s">
         <v>40</v>
@@ -1104,8 +1360,9 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D46" s="6"/>
+    </row>
+    <row r="47" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3"/>
       <c r="B47" s="1" t="s">
         <v>44</v>
@@ -1113,8 +1370,9 @@
       <c r="C47" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D47" s="6"/>
+    </row>
+    <row r="48" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3"/>
       <c r="B48" s="1" t="s">
         <v>46</v>
@@ -1122,8 +1380,9 @@
       <c r="C48" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D48" s="6"/>
+    </row>
+    <row r="49" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>55</v>
       </c>
@@ -1133,8 +1392,11 @@
       <c r="C49" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D49" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3"/>
       <c r="B50" s="1" t="s">
         <v>38</v>
@@ -1142,8 +1404,9 @@
       <c r="C50" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D50" s="6"/>
+    </row>
+    <row r="51" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3"/>
       <c r="B51" s="1" t="s">
         <v>40</v>
@@ -1151,8 +1414,9 @@
       <c r="C51" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D51" s="6"/>
+    </row>
+    <row r="52" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3"/>
       <c r="B52" s="1" t="s">
         <v>57</v>
@@ -1160,8 +1424,9 @@
       <c r="C52" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D52" s="6"/>
+    </row>
+    <row r="53" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3"/>
       <c r="B53" s="1" t="s">
         <v>58</v>
@@ -1169,27 +1434,31 @@
       <c r="C53" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D53" s="6"/>
+    </row>
+    <row r="54" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
-    </row>
-    <row r="62" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D61" s="4"/>
+    </row>
+    <row r="62" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
-    </row>
-    <row r="63" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D62" s="4"/>
+    </row>
+    <row r="63" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
-    </row>
-    <row r="64" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D63" s="4"/>
+    </row>
+    <row r="64" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
         <v>50</v>
       </c>
@@ -1199,18 +1468,23 @@
       <c r="C64" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D64" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
-    </row>
-    <row r="66" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D65" s="5"/>
+    </row>
+    <row r="66" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
-    </row>
-    <row r="67" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D66" s="5"/>
+    </row>
+    <row r="67" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>60</v>
       </c>
@@ -1220,8 +1494,11 @@
       <c r="C67" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D67" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3"/>
       <c r="B68" s="1" t="s">
         <v>38</v>
@@ -1229,8 +1506,9 @@
       <c r="C68" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D68" s="6"/>
+    </row>
+    <row r="69" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3"/>
       <c r="B69" s="1" t="s">
         <v>40</v>
@@ -1238,8 +1516,9 @@
       <c r="C69" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D69" s="6"/>
+    </row>
+    <row r="70" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3"/>
       <c r="B70" s="1" t="s">
         <v>63</v>
@@ -1247,8 +1526,9 @@
       <c r="C70" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D70" s="6"/>
+    </row>
+    <row r="71" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3"/>
       <c r="B71" s="1" t="s">
         <v>61</v>
@@ -1256,8 +1536,9 @@
       <c r="C71" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D71" s="6"/>
+    </row>
+    <row r="72" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3"/>
       <c r="B72" s="1" t="s">
         <v>64</v>
@@ -1265,8 +1546,9 @@
       <c r="C72" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D72" s="6"/>
+    </row>
+    <row r="73" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3"/>
       <c r="B73" s="1" t="s">
         <v>65</v>
@@ -1274,8 +1556,9 @@
       <c r="C73" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D73" s="6"/>
+    </row>
+    <row r="74" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3"/>
       <c r="B74" s="1" t="s">
         <v>66</v>
@@ -1283,8 +1566,9 @@
       <c r="C74" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D74" s="6"/>
+    </row>
+    <row r="75" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>68</v>
       </c>
@@ -1294,8 +1578,11 @@
       <c r="C75" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D75" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3"/>
       <c r="B76" s="1" t="s">
         <v>38</v>
@@ -1303,8 +1590,9 @@
       <c r="C76" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D76" s="6"/>
+    </row>
+    <row r="77" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3"/>
       <c r="B77" s="1" t="s">
         <v>40</v>
@@ -1312,8 +1600,9 @@
       <c r="C77" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D77" s="6"/>
+    </row>
+    <row r="78" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3"/>
       <c r="B78" s="1" t="s">
         <v>41</v>
@@ -1321,8 +1610,9 @@
       <c r="C78" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D78" s="6"/>
+    </row>
+    <row r="79" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>70</v>
       </c>
@@ -1332,8 +1622,11 @@
       <c r="C79" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D79" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3"/>
       <c r="B80" s="1" t="s">
         <v>38</v>
@@ -1341,8 +1634,9 @@
       <c r="C80" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D80" s="6"/>
+    </row>
+    <row r="81" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3"/>
       <c r="B81" s="1" t="s">
         <v>40</v>
@@ -1350,8 +1644,9 @@
       <c r="C81" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D81" s="6"/>
+    </row>
+    <row r="82" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3"/>
       <c r="B82" s="1" t="s">
         <v>71</v>
@@ -1359,8 +1654,9 @@
       <c r="C82" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D82" s="6"/>
+    </row>
+    <row r="83" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3"/>
       <c r="B83" s="1" t="s">
         <v>72</v>
@@ -1368,27 +1664,31 @@
       <c r="C83" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="90" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="91" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D83" s="6"/>
+    </row>
+    <row r="84" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>74</v>
       </c>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
-    </row>
-    <row r="92" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D91" s="4"/>
+    </row>
+    <row r="92" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
-    </row>
-    <row r="93" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D92" s="4"/>
+    </row>
+    <row r="93" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
-    </row>
-    <row r="94" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D93" s="4"/>
+    </row>
+    <row r="94" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
         <v>50</v>
       </c>
@@ -1398,18 +1698,23 @@
       <c r="C94" s="5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D94" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
-    </row>
-    <row r="96" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D95" s="5"/>
+    </row>
+    <row r="96" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
-    </row>
-    <row r="97" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D96" s="5"/>
+    </row>
+    <row r="97" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="3" t="s">
         <v>75</v>
       </c>
@@ -1419,8 +1724,12 @@
       <c r="C97" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D97" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G97" s="15"/>
+    </row>
+    <row r="98" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="3"/>
       <c r="B98" s="1" t="s">
         <v>38</v>
@@ -1428,8 +1737,10 @@
       <c r="C98" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D98" s="6"/>
+      <c r="G98" s="15"/>
+    </row>
+    <row r="99" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3"/>
       <c r="B99" s="1" t="s">
         <v>40</v>
@@ -1437,8 +1748,10 @@
       <c r="C99" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D99" s="6"/>
+      <c r="G99" s="15"/>
+    </row>
+    <row r="100" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3"/>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -1446,8 +1759,10 @@
       <c r="C100" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D100" s="6"/>
+      <c r="G100" s="15"/>
+    </row>
+    <row r="101" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3"/>
       <c r="B101" s="1" t="s">
         <v>84</v>
@@ -1455,8 +1770,10 @@
       <c r="C101" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D101" s="6"/>
+      <c r="G101" s="15"/>
+    </row>
+    <row r="102" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="3"/>
       <c r="B102" s="1" t="s">
         <v>85</v>
@@ -1464,8 +1781,10 @@
       <c r="C102" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D102" s="6"/>
+      <c r="G102" s="15"/>
+    </row>
+    <row r="103" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
         <v>11</v>
       </c>
@@ -1475,8 +1794,12 @@
       <c r="C103" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D103" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G103" s="15"/>
+    </row>
+    <row r="104" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="3"/>
       <c r="B104" s="1" t="s">
         <v>78</v>
@@ -1484,8 +1807,9 @@
       <c r="C104" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D104" s="6"/>
+    </row>
+    <row r="105" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="3"/>
       <c r="B105" s="1" t="s">
         <v>79</v>
@@ -1493,8 +1817,9 @@
       <c r="C105" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D105" s="6"/>
+    </row>
+    <row r="106" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3"/>
       <c r="B106" s="1" t="s">
         <v>80</v>
@@ -1502,8 +1827,9 @@
       <c r="C106" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D106" s="6"/>
+    </row>
+    <row r="107" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>82</v>
       </c>
@@ -1513,8 +1839,11 @@
       <c r="C107" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D107" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="3"/>
       <c r="B108" s="1" t="s">
         <v>78</v>
@@ -1522,8 +1851,9 @@
       <c r="C108" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D108" s="6"/>
+    </row>
+    <row r="109" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3"/>
       <c r="B109" s="1" t="s">
         <v>79</v>
@@ -1531,8 +1861,9 @@
       <c r="C109" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D109" s="6"/>
+    </row>
+    <row r="110" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3"/>
       <c r="B110" s="1" t="s">
         <v>83</v>
@@ -1540,8 +1871,9 @@
       <c r="C110" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D110" s="6"/>
+    </row>
+    <row r="111" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3"/>
       <c r="B111" s="1" t="s">
         <v>90</v>
@@ -1549,291 +1881,659 @@
       <c r="C111" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D111" s="6"/>
+    </row>
+    <row r="112" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3"/>
       <c r="B112" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="6"/>
+    </row>
+    <row r="113" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="3"/>
+      <c r="B113" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D113" s="6"/>
+    </row>
+    <row r="114" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B113" s="1" t="s">
+      <c r="B114" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C114" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A114" s="3"/>
-      <c r="B114" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D114" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E114" s="19"/>
+    </row>
+    <row r="115" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3"/>
       <c r="B115" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="D115" s="6"/>
+      <c r="E115" s="19"/>
+    </row>
+    <row r="116" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3"/>
       <c r="B116" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D116" s="6"/>
+      <c r="E116" s="19"/>
+    </row>
+    <row r="117" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3"/>
       <c r="B117" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D117" s="6"/>
+      <c r="E117" s="19"/>
+    </row>
+    <row r="118" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="3"/>
+      <c r="B118" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C117" s="2" t="s">
+      <c r="C118" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D118" s="6"/>
+      <c r="E118" s="19"/>
+    </row>
+    <row r="119" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B118" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C119" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="3"/>
-      <c r="B119" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D119" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E119" s="19"/>
+    </row>
+    <row r="120" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3"/>
       <c r="B120" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D120" s="6"/>
+      <c r="E120" s="19"/>
+    </row>
+    <row r="121" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="3"/>
+      <c r="B121" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C121" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="3"/>
-      <c r="B121" s="11" t="s">
+      <c r="D121" s="6"/>
+      <c r="E121" s="19"/>
+    </row>
+    <row r="122" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A122" s="3"/>
+      <c r="B122" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D122" s="6"/>
+      <c r="E122" s="19"/>
+    </row>
+    <row r="123" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="3"/>
+      <c r="B123" s="6"/>
+      <c r="C123" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="3"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="2" t="s">
+      <c r="D123" s="6"/>
+      <c r="E123" s="19"/>
+    </row>
+    <row r="124" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="3"/>
+      <c r="B124" s="6" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="3"/>
-      <c r="B123" s="11" t="s">
+      <c r="C124" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="D124" s="6"/>
+      <c r="E124" s="19"/>
+    </row>
+    <row r="125" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="3"/>
+      <c r="B125" s="6"/>
+      <c r="C125" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D125" s="6"/>
+      <c r="E125" s="19"/>
+    </row>
+    <row r="126" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A124" s="3"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A125" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="B126" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C126" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="3"/>
-      <c r="B126" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D126" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E126" s="19"/>
+    </row>
+    <row r="127" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3"/>
       <c r="B127" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+      <c r="D127" s="6"/>
+      <c r="E127" s="19"/>
+    </row>
+    <row r="128" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3"/>
       <c r="B128" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>79</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D128" s="6"/>
+      <c r="E128" s="19"/>
+    </row>
+    <row r="129" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3"/>
       <c r="B129" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D129" s="6"/>
+      <c r="E129" s="19"/>
+    </row>
+    <row r="130" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3"/>
       <c r="B130" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D130" s="6"/>
+      <c r="E130" s="19"/>
+    </row>
+    <row r="131" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="3"/>
+      <c r="B131" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="137" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="138" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-    </row>
-    <row r="139" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-    </row>
-    <row r="140" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-    </row>
-    <row r="141" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A141" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A142" s="5"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="5"/>
-    </row>
-    <row r="143" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A143" s="5"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5"/>
-    </row>
-    <row r="144" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A144" s="3" t="s">
-        <v>106</v>
-      </c>
+      <c r="D131" s="6"/>
+      <c r="E131" s="19"/>
+    </row>
+    <row r="132" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E132" s="19"/>
+    </row>
+    <row r="133" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="3"/>
+      <c r="B133" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D133" s="14"/>
+      <c r="E133" s="19"/>
+    </row>
+    <row r="134" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="3"/>
+      <c r="B134" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D134" s="14"/>
+      <c r="E134" s="19"/>
+    </row>
+    <row r="135" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="3"/>
+      <c r="B135" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D135" s="14"/>
+      <c r="E135" s="19"/>
+    </row>
+    <row r="136" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="3"/>
+      <c r="B136" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D136" s="14"/>
+      <c r="E136" s="19"/>
+    </row>
+    <row r="137" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="3"/>
+      <c r="B138" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D138" s="14"/>
+    </row>
+    <row r="139" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="3"/>
+      <c r="B139" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D139" s="14"/>
+    </row>
+    <row r="140" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="3"/>
+      <c r="B140" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D140" s="14"/>
+    </row>
+    <row r="141" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="3"/>
+      <c r="B141" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D141" s="14"/>
+    </row>
+    <row r="142" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E142" s="19"/>
+    </row>
+    <row r="143" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="3"/>
+      <c r="B143" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D143" s="6"/>
+      <c r="E143" s="19"/>
+    </row>
+    <row r="144" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="3"/>
       <c r="B144" s="1" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="D144" s="6"/>
+      <c r="E144" s="19"/>
+    </row>
+    <row r="145" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3"/>
       <c r="B145" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A146" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D145" s="6"/>
+      <c r="E145" s="19"/>
+    </row>
+    <row r="146" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="B146" s="1" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E146" s="19"/>
+    </row>
+    <row r="147" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3"/>
       <c r="B147" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D147" s="6"/>
+      <c r="E147" s="19"/>
+    </row>
+    <row r="148" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3"/>
       <c r="B148" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D148" s="6"/>
+      <c r="E148" s="19"/>
+    </row>
+    <row r="149" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="3"/>
       <c r="B149" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D149" s="6"/>
+      <c r="E149" s="19"/>
+    </row>
+    <row r="150" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="3"/>
+      <c r="B150" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D150" s="6"/>
+      <c r="E150" s="19"/>
+    </row>
+    <row r="151" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="3"/>
+      <c r="B151" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D151" s="6"/>
+      <c r="E151" s="19"/>
+    </row>
+    <row r="152" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="3"/>
+      <c r="B152" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D152" s="6"/>
+      <c r="E152" s="19"/>
+    </row>
+    <row r="153" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D157" s="12"/>
+      <c r="E157" s="21"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D158" s="12"/>
+      <c r="E158" s="21"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D159" s="12"/>
+      <c r="E159" s="21"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D160" s="12"/>
+      <c r="E160" s="21"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D161" s="12"/>
+      <c r="E161" s="21"/>
+    </row>
+    <row r="162" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D162" s="12"/>
+      <c r="E162" s="21"/>
+    </row>
+    <row r="163" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A163" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+    </row>
+    <row r="164" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
+      <c r="C164" s="4"/>
+      <c r="D164" s="4"/>
+    </row>
+    <row r="165" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
+      <c r="C165" s="4"/>
+      <c r="D165" s="4"/>
+    </row>
+    <row r="166" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B166" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D166" s="16" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="17"/>
+      <c r="B167" s="17"/>
+      <c r="C167" s="17"/>
+      <c r="D167" s="17"/>
+    </row>
+    <row r="168" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A168" s="18"/>
+      <c r="B168" s="18"/>
+      <c r="C168" s="18"/>
+      <c r="D168" s="18"/>
+    </row>
+    <row r="169" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A169" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A170" s="8"/>
+      <c r="B170" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D170" s="20"/>
+    </row>
+    <row r="171" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A171" s="8"/>
+      <c r="B171" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D171" s="20"/>
+    </row>
+    <row r="172" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A172" s="8"/>
+      <c r="B172" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" s="20"/>
+    </row>
+    <row r="173" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A173" s="8"/>
+      <c r="B173" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D173" s="20"/>
+    </row>
+    <row r="174" spans="1:5" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="9"/>
+      <c r="B174" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C149" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+      <c r="D174" s="11"/>
+    </row>
+    <row r="175" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="A144:A149"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="A118:A124"/>
-    <mergeCell ref="A125:A130"/>
-    <mergeCell ref="A138:C140"/>
-    <mergeCell ref="A141:A143"/>
-    <mergeCell ref="B141:B143"/>
-    <mergeCell ref="C141:C143"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="A107:A112"/>
-    <mergeCell ref="A113:A117"/>
-    <mergeCell ref="B121:B122"/>
+  <mergeCells count="78">
+    <mergeCell ref="D169:D174"/>
+    <mergeCell ref="A169:A174"/>
+    <mergeCell ref="D146:D152"/>
+    <mergeCell ref="A146:A152"/>
+    <mergeCell ref="D142:D145"/>
+    <mergeCell ref="A142:A145"/>
+    <mergeCell ref="A163:D165"/>
+    <mergeCell ref="A166:A168"/>
+    <mergeCell ref="B166:B168"/>
+    <mergeCell ref="C166:C168"/>
+    <mergeCell ref="D166:D168"/>
+    <mergeCell ref="D97:D102"/>
+    <mergeCell ref="D103:D106"/>
+    <mergeCell ref="D107:D113"/>
+    <mergeCell ref="D114:D118"/>
+    <mergeCell ref="D132:D136"/>
+    <mergeCell ref="D137:D141"/>
+    <mergeCell ref="D119:D125"/>
+    <mergeCell ref="D126:D131"/>
+    <mergeCell ref="D67:D74"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="D79:D83"/>
+    <mergeCell ref="D94:D96"/>
+    <mergeCell ref="A91:D93"/>
+    <mergeCell ref="D36:D39"/>
+    <mergeCell ref="D40:D43"/>
+    <mergeCell ref="D44:D48"/>
+    <mergeCell ref="D49:D53"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="A61:D63"/>
+    <mergeCell ref="D13:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="A28:D30"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="B124:B125"/>
+    <mergeCell ref="A119:A125"/>
+    <mergeCell ref="A126:A131"/>
+    <mergeCell ref="A132:A136"/>
+    <mergeCell ref="A137:A141"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A107:A113"/>
+    <mergeCell ref="A114:A118"/>
+    <mergeCell ref="B122:B123"/>
     <mergeCell ref="A36:A39"/>
     <mergeCell ref="A40:A43"/>
     <mergeCell ref="B36:B37"/>
@@ -1845,28 +2545,28 @@
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="A13:A20"/>
-    <mergeCell ref="A28:C30"/>
+    <mergeCell ref="A103:A106"/>
+    <mergeCell ref="A67:A74"/>
+    <mergeCell ref="A75:A78"/>
+    <mergeCell ref="A79:A83"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="D4:D6"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D10:D12"/>
+    <mergeCell ref="A97:A102"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="A49:A53"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:C66"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="A31:A33"/>
     <mergeCell ref="B31:B33"/>
     <mergeCell ref="C31:C33"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="A61:C63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="A97:A102"/>
-    <mergeCell ref="A103:A106"/>
-    <mergeCell ref="A67:A74"/>
-    <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="A91:C93"/>
-    <mergeCell ref="A94:A96"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="C94:C96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
